--- a/experiment_results/wedos_grid/rtt_bursts_S4_atk10pct_wu300000_stage1a_rep1.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S4_atk10pct_wu300000_stage1a_rep1.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1226182</t>
+          <t>710292</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1463872</t>
+          <t>755465</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1610593</t>
+          <t>857013</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1738083</t>
+          <t>882954</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1801147</t>
+          <t>920078</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1905509</t>
+          <t>987316</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2002544</t>
+          <t>1017113</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2059750</t>
+          <t>1044522</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2116354</t>
+          <t>1073717</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2179256</t>
+          <t>1107424</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2235451</t>
+          <t>1129912</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2279995</t>
+          <t>1151968</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2340719</t>
+          <t>1190637</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2379481</t>
+          <t>1190730</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
